--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350464</v>
+        <v>130350508</v>
       </c>
       <c r="B4" t="n">
-        <v>91728</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +905,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595443</v>
+        <v>595458</v>
       </c>
       <c r="R4" t="n">
-        <v>6397200</v>
+        <v>6397259</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Under granlåga</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +986,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350508</v>
+        <v>130350464</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>91731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,31 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595458</v>
+        <v>595443</v>
       </c>
       <c r="R5" t="n">
-        <v>6397259</v>
+        <v>6397200</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spår efter födosök</t>
+          <t>Under granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,6 +1099,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130350552</v>
       </c>
       <c r="B3" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350508</v>
+        <v>130350464</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>91757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,31 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595458</v>
+        <v>595443</v>
       </c>
       <c r="R4" t="n">
-        <v>6397259</v>
+        <v>6397200</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spår efter födosök</t>
+          <t>Under granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350464</v>
+        <v>130350508</v>
       </c>
       <c r="B5" t="n">
-        <v>91731</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,34 +1019,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595443</v>
+        <v>595458</v>
       </c>
       <c r="R5" t="n">
-        <v>6397200</v>
+        <v>6397259</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Under granlåga</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>130350486</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350464</v>
+        <v>130350508</v>
       </c>
       <c r="B4" t="n">
-        <v>91757</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +905,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -940,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595443</v>
+        <v>595458</v>
       </c>
       <c r="R4" t="n">
-        <v>6397200</v>
+        <v>6397259</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Under granlåga</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +986,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350508</v>
+        <v>130350464</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>91758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,31 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595458</v>
+        <v>595443</v>
       </c>
       <c r="R5" t="n">
-        <v>6397259</v>
+        <v>6397200</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spår efter födosök</t>
+          <t>Under granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,6 +1099,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130350464</v>
       </c>
       <c r="B5" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>106018</v>
+        <v>106020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130350552</v>
       </c>
       <c r="B3" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130350508</v>
+        <v>130350464</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>91761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,31 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,13 +940,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595458</v>
+        <v>595443</v>
       </c>
       <c r="R4" t="n">
-        <v>6397259</v>
+        <v>6397200</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +980,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spår efter födosök</t>
+          <t>Under granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130350464</v>
+        <v>130350508</v>
       </c>
       <c r="B5" t="n">
-        <v>91759</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,34 +1019,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595443</v>
+        <v>595458</v>
       </c>
       <c r="R5" t="n">
-        <v>6397200</v>
+        <v>6397259</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1091,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Under granlåga</t>
+          <t>Spår efter födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,7 +1100,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>130350486</v>
       </c>
       <c r="B6" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>106020</v>
+        <v>106024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>106024</v>
+        <v>106037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130350552</v>
       </c>
       <c r="B3" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130350464</v>
       </c>
       <c r="B4" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130350508</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>130350486</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130350552</v>
       </c>
       <c r="B3" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130350464</v>
       </c>
       <c r="B4" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130350508</v>
       </c>
       <c r="B5" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>130350486</v>
       </c>
       <c r="B6" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60491-2025 artfynd.xlsx
+++ b/artfynd/A 60491-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130350536</v>
       </c>
       <c r="B2" t="n">
-        <v>106038</v>
+        <v>106041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130350552</v>
       </c>
       <c r="B3" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130350464</v>
       </c>
       <c r="B4" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>130350508</v>
       </c>
       <c r="B5" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
